--- a/ПВО_список_покупок.xlsx
+++ b/ПВО_список_покупок.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="116">
   <si>
     <t xml:space="preserve">ПВО ОТ КОМАРОВ — полный список комплектующих (рекомендация)</t>
   </si>
@@ -277,7 +277,46 @@
     <t xml:space="preserve">необязательно, но желательно</t>
   </si>
   <si>
-    <t xml:space="preserve">5. ИНСТРУМЕНТЫ — если ещё нет</t>
+    <t xml:space="preserve">5. ОПЦИОНАЛЬНЫЕ МОДУЛИ — украшения по вкусу</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLED-экран SSD1306 0,96" I2C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«экран боевого поста» на турели (вариант B)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">адрес 0x3C; библиотека Adafruit SSD1306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DFPlayer Mini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">озвучка событий голосом/звуками</t>
+  </si>
+  <si>
+    <t xml:space="preserve">библиотека не нужна — протокол в прошивке</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Динамик 3 Вт 4–8 Ом</t>
+  </si>
+  <si>
+    <t xml:space="preserve">к DFPlayer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">или маленький «квадратик» 2 Вт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">microSD 1–8 ГБ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дорожки /mp3/0001..0005.mp3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">подойдёт любая старая</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. ИНСТРУМЕНТЫ — если ещё нет</t>
   </si>
   <si>
     <t xml:space="preserve">Термоклеевой пистолет + стержни</t>
@@ -320,6 +359,9 @@
   </si>
   <si>
     <t xml:space="preserve">Полная программа: базовый + A + B + зрение C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Опциональные модули (по вкусу)</t>
   </si>
   <si>
     <t xml:space="preserve">Инструменты (если совсем с нуля)</t>
@@ -897,7 +939,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4.5"/>
@@ -1794,61 +1836,65 @@
         <v>87</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>450</v>
+        <v>250</v>
       </c>
       <c r="F46" s="11" t="n">
         <f aca="false">C46*E46</f>
-        <v>450</v>
+        <v>250</v>
       </c>
       <c r="G46" s="12"/>
-      <c r="H46" s="13"/>
+      <c r="H46" s="13" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="n">
         <v>26</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C47" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="F47" s="11" t="n">
         <f aca="false">C47*E47</f>
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="G47" s="12"/>
-      <c r="H47" s="13"/>
+      <c r="H47" s="13" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="n">
         <v>27</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C48" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>800</v>
+        <v>120</v>
       </c>
       <c r="F48" s="11" t="n">
         <f aca="false">C48*E48</f>
-        <v>800</v>
+        <v>120</v>
       </c>
       <c r="G48" s="12"/>
       <c r="H48" s="13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1856,13 +1902,13 @@
         <v>28</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C49" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E49" s="10" t="n">
         <v>250</v>
@@ -1872,7 +1918,9 @@
         <v>250</v>
       </c>
       <c r="G49" s="12"/>
-      <c r="H49" s="13"/>
+      <c r="H49" s="13" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="14" t="s">
@@ -1884,112 +1932,274 @@
       <c r="E50" s="14"/>
       <c r="F50" s="15" t="n">
         <f aca="false">SUM(F46:F49)</f>
-        <v>2000</v>
+        <v>770</v>
       </c>
       <c r="G50" s="16"/>
       <c r="H50" s="16"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="B52" s="17"/>
-      <c r="C52" s="17"/>
-      <c r="D52" s="17"/>
-      <c r="E52" s="17"/>
-      <c r="F52" s="17"/>
-      <c r="G52" s="17"/>
-      <c r="H52" s="17"/>
-    </row>
-    <row r="53" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="B53" s="18"/>
-      <c r="C53" s="18"/>
-      <c r="D53" s="18"/>
-      <c r="E53" s="18"/>
-      <c r="F53" s="19" t="n">
+    <row r="52" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="3"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C54" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>450</v>
+      </c>
+      <c r="F54" s="11" t="n">
+        <f aca="false">C54*E54</f>
+        <v>450</v>
+      </c>
+      <c r="G54" s="12"/>
+      <c r="H54" s="13"/>
+    </row>
+    <row r="55" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C55" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>500</v>
+      </c>
+      <c r="F55" s="11" t="n">
+        <f aca="false">C55*E55</f>
+        <v>500</v>
+      </c>
+      <c r="G55" s="12"/>
+      <c r="H55" s="13"/>
+    </row>
+    <row r="56" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C56" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>800</v>
+      </c>
+      <c r="F56" s="11" t="n">
+        <f aca="false">C56*E56</f>
+        <v>800</v>
+      </c>
+      <c r="G56" s="12"/>
+      <c r="H56" s="13" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C57" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>250</v>
+      </c>
+      <c r="F57" s="11" t="n">
+        <f aca="false">C57*E57</f>
+        <v>250</v>
+      </c>
+      <c r="G57" s="12"/>
+      <c r="H57" s="13"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B58" s="14"/>
+      <c r="C58" s="14"/>
+      <c r="D58" s="14"/>
+      <c r="E58" s="14"/>
+      <c r="F58" s="15" t="n">
+        <f aca="false">SUM(F54:F57)</f>
+        <v>2000</v>
+      </c>
+      <c r="G58" s="16"/>
+      <c r="H58" s="16"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="B60" s="17"/>
+      <c r="C60" s="17"/>
+      <c r="D60" s="17"/>
+      <c r="E60" s="17"/>
+      <c r="F60" s="17"/>
+      <c r="G60" s="17"/>
+      <c r="H60" s="17"/>
+    </row>
+    <row r="61" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="B61" s="18"/>
+      <c r="C61" s="18"/>
+      <c r="D61" s="18"/>
+      <c r="E61" s="18"/>
+      <c r="F61" s="19" t="n">
         <f aca="false">F14+F25</f>
         <v>3740</v>
       </c>
-      <c r="G53" s="7"/>
-      <c r="H53" s="20"/>
-    </row>
-    <row r="54" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="21" t="s">
-        <v>97</v>
-      </c>
-      <c r="B54" s="21"/>
-      <c r="C54" s="21"/>
-      <c r="D54" s="21"/>
-      <c r="E54" s="21"/>
-      <c r="F54" s="15" t="n">
+      <c r="G61" s="7"/>
+      <c r="H61" s="20"/>
+    </row>
+    <row r="62" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="B62" s="21"/>
+      <c r="C62" s="21"/>
+      <c r="D62" s="21"/>
+      <c r="E62" s="21"/>
+      <c r="F62" s="15" t="n">
         <f aca="false">F14+F33</f>
         <v>2190</v>
       </c>
-      <c r="G54" s="7"/>
-      <c r="H54" s="20"/>
-    </row>
-    <row r="55" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="B55" s="21"/>
-      <c r="C55" s="21"/>
-      <c r="D55" s="21"/>
-      <c r="E55" s="21"/>
-      <c r="F55" s="15" t="n">
+      <c r="G62" s="7"/>
+      <c r="H62" s="20"/>
+    </row>
+    <row r="63" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="B63" s="21"/>
+      <c r="C63" s="21"/>
+      <c r="D63" s="21"/>
+      <c r="E63" s="21"/>
+      <c r="F63" s="15" t="n">
         <f aca="false">F14+F25+F33</f>
         <v>4530</v>
       </c>
-      <c r="G55" s="7"/>
-      <c r="H55" s="20"/>
-    </row>
-    <row r="56" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="B56" s="21"/>
-      <c r="C56" s="21"/>
-      <c r="D56" s="21"/>
-      <c r="E56" s="21"/>
-      <c r="F56" s="15" t="n">
+      <c r="G63" s="7"/>
+      <c r="H63" s="20"/>
+    </row>
+    <row r="64" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="B64" s="21"/>
+      <c r="C64" s="21"/>
+      <c r="D64" s="21"/>
+      <c r="E64" s="21"/>
+      <c r="F64" s="15" t="n">
         <f aca="false">F14+F25+F33+F42</f>
         <v>13830</v>
       </c>
-      <c r="G56" s="7"/>
-      <c r="H56" s="20"/>
-    </row>
-    <row r="57" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="B57" s="21"/>
-      <c r="C57" s="21"/>
-      <c r="D57" s="21"/>
-      <c r="E57" s="21"/>
-      <c r="F57" s="15" t="n">
+      <c r="G64" s="7"/>
+      <c r="H64" s="20"/>
+    </row>
+    <row r="65" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="B65" s="21"/>
+      <c r="C65" s="21"/>
+      <c r="D65" s="21"/>
+      <c r="E65" s="21"/>
+      <c r="F65" s="15" t="n">
         <f aca="false">F50</f>
+        <v>770</v>
+      </c>
+      <c r="G65" s="7"/>
+      <c r="H65" s="20"/>
+    </row>
+    <row r="66" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="B66" s="21"/>
+      <c r="C66" s="21"/>
+      <c r="D66" s="21"/>
+      <c r="E66" s="21"/>
+      <c r="F66" s="15" t="n">
+        <f aca="false">F58</f>
         <v>2000</v>
       </c>
-      <c r="G57" s="7"/>
-      <c r="H57" s="20"/>
-    </row>
-    <row r="59" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="22" t="s">
-        <v>101</v>
-      </c>
-      <c r="B59" s="22"/>
-      <c r="C59" s="22"/>
-      <c r="D59" s="22"/>
-      <c r="E59" s="22"/>
-      <c r="F59" s="22"/>
-      <c r="G59" s="22"/>
-      <c r="H59" s="22"/>
+      <c r="G66" s="7"/>
+      <c r="H66" s="20"/>
+    </row>
+    <row r="68" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B68" s="22"/>
+      <c r="C68" s="22"/>
+      <c r="D68" s="22"/>
+      <c r="E68" s="22"/>
+      <c r="F68" s="22"/>
+      <c r="G68" s="22"/>
+      <c r="H68" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="22">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A4:H4"/>
@@ -2003,12 +2213,15 @@
     <mergeCell ref="A44:H44"/>
     <mergeCell ref="A50:E50"/>
     <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A53:E53"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A56:E56"/>
-    <mergeCell ref="A57:E57"/>
-    <mergeCell ref="A59:H59"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A68:H68"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/ПВО_список_покупок.xlsx
+++ b/ПВО_список_покупок.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="127">
   <si>
     <t xml:space="preserve">ПВО ОТ КОМАРОВ — полный список комплектующих (рекомендация)</t>
   </si>
@@ -277,7 +277,37 @@
     <t xml:space="preserve">необязательно, но желательно</t>
   </si>
   <si>
-    <t xml:space="preserve">5. ОПЦИОНАЛЬНЫЕ МОДУЛИ — украшения по вкусу</t>
+    <t xml:space="preserve">5. ИК-ОХОТА — вариант D «Комар-Ф» (слияние B + C, глава 13)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ИК-модуль подсветки 850 нм (плата от камер наблюдения)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">невидимая подсветка мелочи: мошки, комары</t>
+  </si>
+  <si>
+    <t xml:space="preserve">или 3–6 ИК-диодов 850 нм кольцом вокруг объектива; 940 нм камера видит заметно хуже</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Камера БЕЗ ИК-фильтра</t>
+  </si>
+  <si>
+    <t xml:space="preserve">обязательна для ИК-охоты (обычные камеры ИК не видят)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 ₽ — снять фильтр с вебки из раздела 4; или готовая Raspberry Pi Camera NoIR (CSI) ~1500–2500 ₽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOSFET 2N7000 или AO3400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ключ ИК-платы при токе больше ~150 мА</t>
+  </si>
+  <si>
+    <t xml:space="preserve">мелкой подсветке (до ~150 мА) хватит 2N2222 из раздела 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. ОПЦИОНАЛЬНЫЕ МОДУЛИ — украшения по вкусу</t>
   </si>
   <si>
     <t xml:space="preserve">OLED-экран SSD1306 0,96" I2C</t>
@@ -316,7 +346,7 @@
     <t xml:space="preserve">подойдёт любая старая</t>
   </si>
   <si>
-    <t xml:space="preserve">6. ИНСТРУМЕНТЫ — если ещё нет</t>
+    <t xml:space="preserve">7. ИНСТРУМЕНТЫ — если ещё нет</t>
   </si>
   <si>
     <t xml:space="preserve">Термоклеевой пистолет + стержни</t>
@@ -359,6 +389,9 @@
   </si>
   <si>
     <t xml:space="preserve">Полная программа: базовый + A + B + зрение C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Слияние D «Комар-Ф»: базовый + B + зрение C + ИК-охота</t>
   </si>
   <si>
     <t xml:space="preserve">Опциональные модули (по вкусу)</t>
@@ -939,7 +972,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4.5"/>
@@ -1861,11 +1894,11 @@
         <v>90</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F47" s="11" t="n">
         <f aca="false">C47*E47</f>
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="G47" s="12"/>
       <c r="H47" s="13" t="s">
@@ -1886,93 +1919,93 @@
         <v>93</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="F48" s="11" t="n">
         <f aca="false">C48*E48</f>
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="G48" s="12"/>
       <c r="H48" s="13" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="6" t="n">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B49" s="14"/>
+      <c r="C49" s="14"/>
+      <c r="D49" s="14"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="15" t="n">
+        <f aca="false">SUM(F46:F48)</f>
+        <v>270</v>
+      </c>
+      <c r="G49" s="16"/>
+      <c r="H49" s="16"/>
+    </row>
+    <row r="51" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="B49" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C49" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" s="9" t="s">
+      <c r="B53" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E49" s="10" t="n">
+      <c r="C53" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E53" s="10" t="n">
         <v>250</v>
       </c>
-      <c r="F49" s="11" t="n">
-        <f aca="false">C49*E49</f>
+      <c r="F53" s="11" t="n">
+        <f aca="false">C53*E53</f>
         <v>250</v>
       </c>
-      <c r="G49" s="12"/>
-      <c r="H49" s="13" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="15" t="n">
-        <f aca="false">SUM(F46:F49)</f>
-        <v>770</v>
-      </c>
-      <c r="G50" s="16"/>
-      <c r="H50" s="16"/>
-    </row>
-    <row r="52" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="3" t="s">
+      <c r="G53" s="12"/>
+      <c r="H53" s="13" t="s">
         <v>98</v>
-      </c>
-      <c r="B52" s="3"/>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3"/>
-      <c r="H52" s="3"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H53" s="5" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1989,217 +2022,360 @@
         <v>100</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="F54" s="11" t="n">
         <f aca="false">C54*E54</f>
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="G54" s="12"/>
-      <c r="H54" s="13"/>
+      <c r="H54" s="13" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="6" t="n">
         <v>30</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C55" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E55" s="10" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="F55" s="11" t="n">
         <f aca="false">C55*E55</f>
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="G55" s="12"/>
-      <c r="H55" s="13"/>
+      <c r="H55" s="13" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="n">
         <v>31</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C56" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E56" s="10" t="n">
-        <v>800</v>
+        <v>250</v>
       </c>
       <c r="F56" s="11" t="n">
         <f aca="false">C56*E56</f>
-        <v>800</v>
+        <v>250</v>
       </c>
       <c r="G56" s="12"/>
       <c r="H56" s="13" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="6" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B57" s="14"/>
+      <c r="C57" s="14"/>
+      <c r="D57" s="14"/>
+      <c r="E57" s="14"/>
+      <c r="F57" s="15" t="n">
+        <f aca="false">SUM(F53:F56)</f>
+        <v>770</v>
+      </c>
+      <c r="G57" s="16"/>
+      <c r="H57" s="16"/>
+    </row>
+    <row r="59" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H60" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="B57" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C57" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="E57" s="10" t="n">
+      <c r="B61" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C61" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="E61" s="10" t="n">
+        <v>450</v>
+      </c>
+      <c r="F61" s="11" t="n">
+        <f aca="false">C61*E61</f>
+        <v>450</v>
+      </c>
+      <c r="G61" s="12"/>
+      <c r="H61" s="13"/>
+    </row>
+    <row r="62" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C62" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>500</v>
+      </c>
+      <c r="F62" s="11" t="n">
+        <f aca="false">C62*E62</f>
+        <v>500</v>
+      </c>
+      <c r="G62" s="12"/>
+      <c r="H62" s="13"/>
+    </row>
+    <row r="63" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C63" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>800</v>
+      </c>
+      <c r="F63" s="11" t="n">
+        <f aca="false">C63*E63</f>
+        <v>800</v>
+      </c>
+      <c r="G63" s="12"/>
+      <c r="H63" s="13" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C64" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E64" s="10" t="n">
         <v>250</v>
       </c>
-      <c r="F57" s="11" t="n">
-        <f aca="false">C57*E57</f>
+      <c r="F64" s="11" t="n">
+        <f aca="false">C64*E64</f>
         <v>250</v>
       </c>
-      <c r="G57" s="12"/>
-      <c r="H57" s="13"/>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="14" t="s">
+      <c r="G64" s="12"/>
+      <c r="H64" s="13"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="15" t="n">
-        <f aca="false">SUM(F54:F57)</f>
+      <c r="B65" s="14"/>
+      <c r="C65" s="14"/>
+      <c r="D65" s="14"/>
+      <c r="E65" s="14"/>
+      <c r="F65" s="15" t="n">
+        <f aca="false">SUM(F61:F64)</f>
         <v>2000</v>
       </c>
-      <c r="G58" s="16"/>
-      <c r="H58" s="16"/>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="B60" s="17"/>
-      <c r="C60" s="17"/>
-      <c r="D60" s="17"/>
-      <c r="E60" s="17"/>
-      <c r="F60" s="17"/>
-      <c r="G60" s="17"/>
-      <c r="H60" s="17"/>
-    </row>
-    <row r="61" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="B61" s="18"/>
-      <c r="C61" s="18"/>
-      <c r="D61" s="18"/>
-      <c r="E61" s="18"/>
-      <c r="F61" s="19" t="n">
+      <c r="G65" s="16"/>
+      <c r="H65" s="16"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="B67" s="17"/>
+      <c r="C67" s="17"/>
+      <c r="D67" s="17"/>
+      <c r="E67" s="17"/>
+      <c r="F67" s="17"/>
+      <c r="G67" s="17"/>
+      <c r="H67" s="17"/>
+    </row>
+    <row r="68" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="B68" s="18"/>
+      <c r="C68" s="18"/>
+      <c r="D68" s="18"/>
+      <c r="E68" s="18"/>
+      <c r="F68" s="19" t="n">
         <f aca="false">F14+F25</f>
         <v>3740</v>
       </c>
-      <c r="G61" s="7"/>
-      <c r="H61" s="20"/>
-    </row>
-    <row r="62" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="21" t="s">
-        <v>110</v>
-      </c>
-      <c r="B62" s="21"/>
-      <c r="C62" s="21"/>
-      <c r="D62" s="21"/>
-      <c r="E62" s="21"/>
-      <c r="F62" s="15" t="n">
+      <c r="G68" s="7"/>
+      <c r="H68" s="20"/>
+    </row>
+    <row r="69" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="B69" s="21"/>
+      <c r="C69" s="21"/>
+      <c r="D69" s="21"/>
+      <c r="E69" s="21"/>
+      <c r="F69" s="15" t="n">
         <f aca="false">F14+F33</f>
         <v>2190</v>
       </c>
-      <c r="G62" s="7"/>
-      <c r="H62" s="20"/>
-    </row>
-    <row r="63" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="B63" s="21"/>
-      <c r="C63" s="21"/>
-      <c r="D63" s="21"/>
-      <c r="E63" s="21"/>
-      <c r="F63" s="15" t="n">
+      <c r="G69" s="7"/>
+      <c r="H69" s="20"/>
+    </row>
+    <row r="70" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="B70" s="21"/>
+      <c r="C70" s="21"/>
+      <c r="D70" s="21"/>
+      <c r="E70" s="21"/>
+      <c r="F70" s="15" t="n">
         <f aca="false">F14+F25+F33</f>
         <v>4530</v>
       </c>
-      <c r="G63" s="7"/>
-      <c r="H63" s="20"/>
-    </row>
-    <row r="64" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="B64" s="21"/>
-      <c r="C64" s="21"/>
-      <c r="D64" s="21"/>
-      <c r="E64" s="21"/>
-      <c r="F64" s="15" t="n">
+      <c r="G70" s="7"/>
+      <c r="H70" s="20"/>
+    </row>
+    <row r="71" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="B71" s="21"/>
+      <c r="C71" s="21"/>
+      <c r="D71" s="21"/>
+      <c r="E71" s="21"/>
+      <c r="F71" s="15" t="n">
         <f aca="false">F14+F25+F33+F42</f>
         <v>13830</v>
       </c>
-      <c r="G64" s="7"/>
-      <c r="H64" s="20"/>
-    </row>
-    <row r="65" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="21" t="s">
-        <v>113</v>
-      </c>
-      <c r="B65" s="21"/>
-      <c r="C65" s="21"/>
-      <c r="D65" s="21"/>
-      <c r="E65" s="21"/>
-      <c r="F65" s="15" t="n">
-        <f aca="false">F50</f>
+      <c r="G71" s="7"/>
+      <c r="H71" s="20"/>
+    </row>
+    <row r="72" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="B72" s="21"/>
+      <c r="C72" s="21"/>
+      <c r="D72" s="21"/>
+      <c r="E72" s="21"/>
+      <c r="F72" s="15" t="n">
+        <f aca="false">F14+F25+F42+F49</f>
+        <v>13310</v>
+      </c>
+      <c r="G72" s="7"/>
+      <c r="H72" s="20"/>
+    </row>
+    <row r="73" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="B73" s="21"/>
+      <c r="C73" s="21"/>
+      <c r="D73" s="21"/>
+      <c r="E73" s="21"/>
+      <c r="F73" s="15" t="n">
+        <f aca="false">F57</f>
         <v>770</v>
       </c>
-      <c r="G65" s="7"/>
-      <c r="H65" s="20"/>
-    </row>
-    <row r="66" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="B66" s="21"/>
-      <c r="C66" s="21"/>
-      <c r="D66" s="21"/>
-      <c r="E66" s="21"/>
-      <c r="F66" s="15" t="n">
-        <f aca="false">F58</f>
+      <c r="G73" s="7"/>
+      <c r="H73" s="20"/>
+    </row>
+    <row r="74" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="B74" s="21"/>
+      <c r="C74" s="21"/>
+      <c r="D74" s="21"/>
+      <c r="E74" s="21"/>
+      <c r="F74" s="15" t="n">
+        <f aca="false">F65</f>
         <v>2000</v>
       </c>
-      <c r="G66" s="7"/>
-      <c r="H66" s="20"/>
-    </row>
-    <row r="68" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="B68" s="22"/>
-      <c r="C68" s="22"/>
-      <c r="D68" s="22"/>
-      <c r="E68" s="22"/>
-      <c r="F68" s="22"/>
-      <c r="G68" s="22"/>
-      <c r="H68" s="22"/>
+      <c r="G74" s="7"/>
+      <c r="H74" s="20"/>
+    </row>
+    <row r="76" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="B76" s="22"/>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="F76" s="22"/>
+      <c r="G76" s="22"/>
+      <c r="H76" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="25">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A4:H4"/>
@@ -2211,17 +2387,20 @@
     <mergeCell ref="A35:H35"/>
     <mergeCell ref="A42:E42"/>
     <mergeCell ref="A44:H44"/>
-    <mergeCell ref="A50:E50"/>
-    <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A60:H60"/>
-    <mergeCell ref="A61:E61"/>
-    <mergeCell ref="A62:E62"/>
-    <mergeCell ref="A63:E63"/>
-    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A59:H59"/>
     <mergeCell ref="A65:E65"/>
-    <mergeCell ref="A66:E66"/>
-    <mergeCell ref="A68:H68"/>
+    <mergeCell ref="A67:H67"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A76:H76"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
